--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1546"/>
+  <dimension ref="A1:H1569"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -40006,7 +40006,7 @@
         <v>5027.0078125</v>
       </c>
       <c r="F1468">
-        <f t="shared" ref="F1468:F1546" si="11">E1468/1000</f>
+        <f t="shared" ref="F1468:F1569" si="11">E1468/1000</f>
         <v>5.0270078125</v>
       </c>
       <c r="G1468">
@@ -42120,6 +42120,627 @@
       </c>
       <c r="H1546">
         <v>42918828</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1547" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B1547">
+        <v>6281.81396484375</v>
+      </c>
+      <c r="C1547">
+        <v>6341.95703125</v>
+      </c>
+      <c r="D1547">
+        <v>6169.06787109375</v>
+      </c>
+      <c r="E1547">
+        <v>6225.044921875</v>
+      </c>
+      <c r="F1547">
+        <f t="shared" si="11"/>
+        <v>6.2250449218749999</v>
+      </c>
+      <c r="G1547">
+        <v>51567556</v>
+      </c>
+      <c r="H1547">
+        <v>51567556</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1548" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B1548">
+        <v>6073.96923828125</v>
+      </c>
+      <c r="C1548">
+        <v>6177.27001953125</v>
+      </c>
+      <c r="D1548">
+        <v>5985.06787109375</v>
+      </c>
+      <c r="E1548">
+        <v>6004.4951171875</v>
+      </c>
+      <c r="F1548">
+        <f t="shared" si="11"/>
+        <v>6.0044951171875001</v>
+      </c>
+      <c r="G1548">
+        <v>49845412</v>
+      </c>
+      <c r="H1548">
+        <v>49845412</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1549" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B1549">
+        <v>5972.2568359375</v>
+      </c>
+      <c r="C1549">
+        <v>6125.169921875</v>
+      </c>
+      <c r="D1549">
+        <v>5947.89990234375</v>
+      </c>
+      <c r="E1549">
+        <v>6024.86181640625</v>
+      </c>
+      <c r="F1549">
+        <f t="shared" si="11"/>
+        <v>6.0248618164062497</v>
+      </c>
+      <c r="G1549">
+        <v>44790660</v>
+      </c>
+      <c r="H1549">
+        <v>44790660</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1550" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B1550">
+        <v>6058.64599609375</v>
+      </c>
+      <c r="C1550">
+        <v>6062.7529296875</v>
+      </c>
+      <c r="D1550">
+        <v>5868.4990234375</v>
+      </c>
+      <c r="E1550">
+        <v>5929.8330078125</v>
+      </c>
+      <c r="F1550">
+        <f t="shared" si="11"/>
+        <v>5.9298330078125003</v>
+      </c>
+      <c r="G1550">
+        <v>42751008</v>
+      </c>
+      <c r="H1550">
+        <v>42751008</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1551" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B1551">
+        <v>5910.52490234375</v>
+      </c>
+      <c r="C1551">
+        <v>5970.384765625</v>
+      </c>
+      <c r="D1551">
+        <v>5815.8388671875</v>
+      </c>
+      <c r="E1551">
+        <v>5870.77099609375</v>
+      </c>
+      <c r="F1551">
+        <f t="shared" si="11"/>
+        <v>5.87077099609375</v>
+      </c>
+      <c r="G1551">
+        <v>40085796</v>
+      </c>
+      <c r="H1551">
+        <v>40085796</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1552" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B1552">
+        <v>5897.27197265625</v>
+      </c>
+      <c r="C1552">
+        <v>5927.2900390625</v>
+      </c>
+      <c r="D1552">
+        <v>5757.2919921875</v>
+      </c>
+      <c r="E1552">
+        <v>5778.94482421875</v>
+      </c>
+      <c r="F1552">
+        <f t="shared" si="11"/>
+        <v>5.7789448242187502</v>
+      </c>
+      <c r="G1552">
+        <v>39717864</v>
+      </c>
+      <c r="H1552">
+        <v>39717864</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1553" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B1553">
+        <v>5827.2099609375</v>
+      </c>
+      <c r="C1553">
+        <v>6031.1318359375</v>
+      </c>
+      <c r="D1553">
+        <v>5758.701171875</v>
+      </c>
+      <c r="E1553">
+        <v>6029.11279296875</v>
+      </c>
+      <c r="F1553">
+        <f t="shared" si="11"/>
+        <v>6.0291127929687498</v>
+      </c>
+      <c r="G1553">
+        <v>44497120</v>
+      </c>
+      <c r="H1553">
+        <v>44497120</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1554" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B1554">
+        <v>6056.13916015625</v>
+      </c>
+      <c r="C1554">
+        <v>6071.39697265625</v>
+      </c>
+      <c r="D1554">
+        <v>5810.12109375</v>
+      </c>
+      <c r="E1554">
+        <v>5810.12109375</v>
+      </c>
+      <c r="F1554">
+        <f t="shared" si="11"/>
+        <v>5.8101210937500003</v>
+      </c>
+      <c r="G1554">
+        <v>51827284</v>
+      </c>
+      <c r="H1554">
+        <v>51827284</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1555" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B1555">
+        <v>5777.5478515625</v>
+      </c>
+      <c r="C1555">
+        <v>5828.6611328125</v>
+      </c>
+      <c r="D1555">
+        <v>5608.5859375</v>
+      </c>
+      <c r="E1555">
+        <v>5650.86279296875</v>
+      </c>
+      <c r="F1555">
+        <f t="shared" si="11"/>
+        <v>5.6508627929687503</v>
+      </c>
+      <c r="G1555">
+        <v>43651820</v>
+      </c>
+      <c r="H1555">
+        <v>43651820</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1556" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B1556">
+        <v>5635.8330078125</v>
+      </c>
+      <c r="C1556">
+        <v>5783.59521484375</v>
+      </c>
+      <c r="D1556">
+        <v>5535.35693359375</v>
+      </c>
+      <c r="E1556">
+        <v>5780.3427734375</v>
+      </c>
+      <c r="F1556">
+        <f t="shared" si="11"/>
+        <v>5.7803427734374999</v>
+      </c>
+      <c r="G1556">
+        <v>43166584</v>
+      </c>
+      <c r="H1556">
+        <v>43166584</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1557" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B1557">
+        <v>5813.44482421875</v>
+      </c>
+      <c r="C1557">
+        <v>5848.3701171875</v>
+      </c>
+      <c r="D1557">
+        <v>5713.76806640625</v>
+      </c>
+      <c r="E1557">
+        <v>5728.96484375</v>
+      </c>
+      <c r="F1557">
+        <f t="shared" si="11"/>
+        <v>5.72896484375</v>
+      </c>
+      <c r="G1557">
+        <v>38904420</v>
+      </c>
+      <c r="H1557">
+        <v>38904420</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1558" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B1558">
+        <v>5628.884765625</v>
+      </c>
+      <c r="C1558">
+        <v>5728.93603515625</v>
+      </c>
+      <c r="D1558">
+        <v>5552.3681640625</v>
+      </c>
+      <c r="E1558">
+        <v>5589.18017578125</v>
+      </c>
+      <c r="F1558">
+        <f t="shared" si="11"/>
+        <v>5.5891801757812498</v>
+      </c>
+      <c r="G1558">
+        <v>39556796</v>
+      </c>
+      <c r="H1558">
+        <v>39556796</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1559" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B1559">
+        <v>5533.7939453125</v>
+      </c>
+      <c r="C1559">
+        <v>5535.833984375</v>
+      </c>
+      <c r="D1559">
+        <v>5235.7548828125</v>
+      </c>
+      <c r="E1559">
+        <v>5277.72802734375</v>
+      </c>
+      <c r="F1559">
+        <f t="shared" si="11"/>
+        <v>5.2777280273437501</v>
+      </c>
+      <c r="G1559">
+        <v>45550628</v>
+      </c>
+      <c r="H1559">
+        <v>45550628</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1560" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B1560">
+        <v>5345.55712890625</v>
+      </c>
+      <c r="C1560">
+        <v>5412.046875</v>
+      </c>
+      <c r="D1560">
+        <v>5142.13818359375</v>
+      </c>
+      <c r="E1560">
+        <v>5249.29296875</v>
+      </c>
+      <c r="F1560">
+        <f t="shared" si="11"/>
+        <v>5.2492929687499998</v>
+      </c>
+      <c r="G1560">
+        <v>44301188</v>
+      </c>
+      <c r="H1560">
+        <v>44301188</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1561" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B1561">
+        <v>5278.505859375</v>
+      </c>
+      <c r="C1561">
+        <v>5546.955078125</v>
+      </c>
+      <c r="D1561">
+        <v>5187.6259765625</v>
+      </c>
+      <c r="E1561">
+        <v>5544.85400390625</v>
+      </c>
+      <c r="F1561">
+        <f t="shared" si="11"/>
+        <v>5.5448540039062504</v>
+      </c>
+      <c r="G1561">
+        <v>48439268</v>
+      </c>
+      <c r="H1561">
+        <v>48439268</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1562" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B1562">
+        <v>5518.4072265625</v>
+      </c>
+      <c r="C1562">
+        <v>5589.5771484375</v>
+      </c>
+      <c r="D1562">
+        <v>5430.0830078125</v>
+      </c>
+      <c r="E1562">
+        <v>5461.0341796875</v>
+      </c>
+      <c r="F1562">
+        <f t="shared" si="11"/>
+        <v>5.4610341796875002</v>
+      </c>
+      <c r="G1562">
+        <v>43276788</v>
+      </c>
+      <c r="H1562">
+        <v>43276788</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1563" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B1563">
+        <v>5481.60400390625</v>
+      </c>
+      <c r="C1563">
+        <v>5518.716796875</v>
+      </c>
+      <c r="D1563">
+        <v>5421.8759765625</v>
+      </c>
+      <c r="E1563">
+        <v>5485.2822265625</v>
+      </c>
+      <c r="F1563">
+        <f t="shared" si="11"/>
+        <v>5.4852822265625001</v>
+      </c>
+      <c r="G1563">
+        <v>35586812</v>
+      </c>
+      <c r="H1563">
+        <v>35586812</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1564" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B1564">
+        <v>5396.23291015625</v>
+      </c>
+      <c r="C1564">
+        <v>5477.1259765625</v>
+      </c>
+      <c r="D1564">
+        <v>5377.39111328125</v>
+      </c>
+      <c r="E1564">
+        <v>5383.4541015625</v>
+      </c>
+      <c r="F1564">
+        <f t="shared" si="11"/>
+        <v>5.3834541015625001</v>
+      </c>
+      <c r="G1564">
+        <v>33836748</v>
+      </c>
+      <c r="H1564">
+        <v>33836748</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1565" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B1565">
+        <v>5390.5458984375</v>
+      </c>
+      <c r="C1565">
+        <v>5535.22119140625</v>
+      </c>
+      <c r="D1565">
+        <v>5352.1669921875</v>
+      </c>
+      <c r="E1565">
+        <v>5535.22119140625</v>
+      </c>
+      <c r="F1565">
+        <f t="shared" si="11"/>
+        <v>5.5352211914062499</v>
+      </c>
+      <c r="G1565">
+        <v>35507276</v>
+      </c>
+      <c r="H1565">
+        <v>35507276</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1566" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B1566">
+        <v>5398.53076171875</v>
+      </c>
+      <c r="C1566">
+        <v>5449.77099609375</v>
+      </c>
+      <c r="D1566">
+        <v>5232.18701171875</v>
+      </c>
+      <c r="E1566">
+        <v>5246.7939453125</v>
+      </c>
+      <c r="F1566">
+        <f t="shared" si="11"/>
+        <v>5.2467939453124997</v>
+      </c>
+      <c r="G1566">
+        <v>32109396</v>
+      </c>
+      <c r="H1566">
+        <v>32109396</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1567" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B1567">
+        <v>5238.166015625</v>
+      </c>
+      <c r="C1567">
+        <v>5331.30810546875</v>
+      </c>
+      <c r="D1567">
+        <v>5129.06298828125</v>
+      </c>
+      <c r="E1567">
+        <v>5293.1240234375</v>
+      </c>
+      <c r="F1567">
+        <f t="shared" si="11"/>
+        <v>5.2931240234374997</v>
+      </c>
+      <c r="G1567">
+        <v>37780464</v>
+      </c>
+      <c r="H1567">
+        <v>37780464</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1568" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B1568">
+        <v>5222.88818359375</v>
+      </c>
+      <c r="C1568">
+        <v>5267.125</v>
+      </c>
+      <c r="D1568">
+        <v>5030.57080078125</v>
+      </c>
+      <c r="E1568">
+        <v>5127.341796875</v>
+      </c>
+      <c r="F1568">
+        <f t="shared" si="11"/>
+        <v>5.1273417968750001</v>
+      </c>
+      <c r="G1568">
+        <v>37105444</v>
+      </c>
+      <c r="H1568">
+        <v>37105444</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1569" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B1569">
+        <v>5295.7900390625</v>
+      </c>
+      <c r="C1569">
+        <v>5361.88916015625</v>
+      </c>
+      <c r="D1569">
+        <v>5237.52197265625</v>
+      </c>
+      <c r="E1569">
+        <v>5237.52197265625</v>
+      </c>
+      <c r="F1569">
+        <f t="shared" si="11"/>
+        <v>5.2375219726562499</v>
+      </c>
+      <c r="G1569">
+        <v>40356296</v>
+      </c>
+      <c r="H1569">
+        <v>40356296</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1569"/>
+  <dimension ref="A1:H1590"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -40006,7 +40006,7 @@
         <v>5027.0078125</v>
       </c>
       <c r="F1468">
-        <f t="shared" ref="F1468:F1569" si="11">E1468/1000</f>
+        <f t="shared" ref="F1468:F1590" si="11">E1468/1000</f>
         <v>5.0270078125</v>
       </c>
       <c r="G1468">
@@ -42741,6 +42741,573 @@
       </c>
       <c r="H1569">
         <v>40356296</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1570" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B1570">
+        <v>5210.087890625</v>
+      </c>
+      <c r="C1570">
+        <v>5238.9921875</v>
+      </c>
+      <c r="D1570">
+        <v>5155.01904296875</v>
+      </c>
+      <c r="E1570">
+        <v>5173.1201171875</v>
+      </c>
+      <c r="F1570">
+        <f t="shared" si="11"/>
+        <v>5.1731201171874996</v>
+      </c>
+      <c r="G1570">
+        <v>31202442</v>
+      </c>
+      <c r="H1570">
+        <v>31202442</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1571" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B1571">
+        <v>5231.71923828125</v>
+      </c>
+      <c r="C1571">
+        <v>5391.203125</v>
+      </c>
+      <c r="D1571">
+        <v>5209.69287109375</v>
+      </c>
+      <c r="E1571">
+        <v>5366.84619140625</v>
+      </c>
+      <c r="F1571">
+        <f t="shared" si="11"/>
+        <v>5.3668461914062497</v>
+      </c>
+      <c r="G1571">
+        <v>33342988</v>
+      </c>
+      <c r="H1571">
+        <v>33342988</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1572" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B1572">
+        <v>5258.7470703125</v>
+      </c>
+      <c r="C1572">
+        <v>5496.9501953125</v>
+      </c>
+      <c r="D1572">
+        <v>5257.5419921875</v>
+      </c>
+      <c r="E1572">
+        <v>5442.66796875</v>
+      </c>
+      <c r="F1572">
+        <f t="shared" si="11"/>
+        <v>5.4426679687500004</v>
+      </c>
+      <c r="G1572">
+        <v>39024460</v>
+      </c>
+      <c r="H1572">
+        <v>39024460</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1573" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B1573">
+        <v>5376.5400390625</v>
+      </c>
+      <c r="C1573">
+        <v>5479.35986328125</v>
+      </c>
+      <c r="D1573">
+        <v>5335.7841796875</v>
+      </c>
+      <c r="E1573">
+        <v>5411.658203125</v>
+      </c>
+      <c r="F1573">
+        <f t="shared" si="11"/>
+        <v>5.4116582031249996</v>
+      </c>
+      <c r="G1573">
+        <v>38970944</v>
+      </c>
+      <c r="H1573">
+        <v>38970944</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1574" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B1574">
+        <v>5434.48681640625</v>
+      </c>
+      <c r="C1574">
+        <v>5521.7578125</v>
+      </c>
+      <c r="D1574">
+        <v>5393.625</v>
+      </c>
+      <c r="E1574">
+        <v>5472.94677734375</v>
+      </c>
+      <c r="F1574">
+        <f t="shared" si="11"/>
+        <v>5.4729467773437497</v>
+      </c>
+      <c r="G1574">
+        <v>39460764</v>
+      </c>
+      <c r="H1574">
+        <v>39460764</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1575" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B1575">
+        <v>5485.09814453125</v>
+      </c>
+      <c r="C1575">
+        <v>5490.80322265625</v>
+      </c>
+      <c r="D1575">
+        <v>5363.43017578125</v>
+      </c>
+      <c r="E1575">
+        <v>5454.31494140625</v>
+      </c>
+      <c r="F1575">
+        <f t="shared" si="11"/>
+        <v>5.45431494140625</v>
+      </c>
+      <c r="G1575">
+        <v>34034332</v>
+      </c>
+      <c r="H1575">
+        <v>34034332</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1576" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B1576">
+        <v>5439.56298828125</v>
+      </c>
+      <c r="C1576">
+        <v>5502.2060546875</v>
+      </c>
+      <c r="D1576">
+        <v>5400.35888671875</v>
+      </c>
+      <c r="E1576">
+        <v>5437.58203125</v>
+      </c>
+      <c r="F1576">
+        <f t="shared" si="11"/>
+        <v>5.4375820312499998</v>
+      </c>
+      <c r="G1576">
+        <v>30825848</v>
+      </c>
+      <c r="H1576">
+        <v>30825848</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1577" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B1577">
+        <v>5428.02880859375</v>
+      </c>
+      <c r="C1577">
+        <v>5527.14208984375</v>
+      </c>
+      <c r="D1577">
+        <v>5427.13720703125</v>
+      </c>
+      <c r="E1577">
+        <v>5502.83984375</v>
+      </c>
+      <c r="F1577">
+        <f t="shared" si="11"/>
+        <v>5.5028398437500003</v>
+      </c>
+      <c r="G1577">
+        <v>28475810</v>
+      </c>
+      <c r="H1577">
+        <v>28475810</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1578" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B1578">
+        <v>5556.15283203125</v>
+      </c>
+      <c r="C1578">
+        <v>5576.47021484375</v>
+      </c>
+      <c r="D1578">
+        <v>5468.52880859375</v>
+      </c>
+      <c r="E1578">
+        <v>5469.13818359375</v>
+      </c>
+      <c r="F1578">
+        <f t="shared" si="11"/>
+        <v>5.46913818359375</v>
+      </c>
+      <c r="G1578">
+        <v>33521038</v>
+      </c>
+      <c r="H1578">
+        <v>33521038</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1579" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B1579">
+        <v>5484.56689453125</v>
+      </c>
+      <c r="C1579">
+        <v>5514.0068359375</v>
+      </c>
+      <c r="D1579">
+        <v>5437.1630859375</v>
+      </c>
+      <c r="E1579">
+        <v>5495.52099609375</v>
+      </c>
+      <c r="F1579">
+        <f t="shared" si="11"/>
+        <v>5.4955209960937497</v>
+      </c>
+      <c r="G1579">
+        <v>28470696</v>
+      </c>
+      <c r="H1579">
+        <v>28470696</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1580" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B1580">
+        <v>5511.48681640625</v>
+      </c>
+      <c r="C1580">
+        <v>5649.83203125</v>
+      </c>
+      <c r="D1580">
+        <v>5492.94287109375</v>
+      </c>
+      <c r="E1580">
+        <v>5649.83203125</v>
+      </c>
+      <c r="F1580">
+        <f t="shared" si="11"/>
+        <v>5.6498320312499999</v>
+      </c>
+      <c r="G1580">
+        <v>31889754</v>
+      </c>
+      <c r="H1580">
+        <v>31889754</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1581" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B1581">
+        <v>5648.22216796875</v>
+      </c>
+      <c r="C1581">
+        <v>5667.5751953125</v>
+      </c>
+      <c r="D1581">
+        <v>5547.58203125</v>
+      </c>
+      <c r="E1581">
+        <v>5606.126953125</v>
+      </c>
+      <c r="F1581">
+        <f t="shared" si="11"/>
+        <v>5.606126953125</v>
+      </c>
+      <c r="G1581">
+        <v>32508112</v>
+      </c>
+      <c r="H1581">
+        <v>32508112</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1582" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B1582">
+        <v>5493.31689453125</v>
+      </c>
+      <c r="C1582">
+        <v>5493.31689453125</v>
+      </c>
+      <c r="D1582">
+        <v>5268.7900390625</v>
+      </c>
+      <c r="E1582">
+        <v>5287.7001953125</v>
+      </c>
+      <c r="F1582">
+        <f t="shared" si="11"/>
+        <v>5.2877001953124996</v>
+      </c>
+      <c r="G1582">
+        <v>35052376</v>
+      </c>
+      <c r="H1582">
+        <v>35052376</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1583" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B1583">
+        <v>5337.8662109375</v>
+      </c>
+      <c r="C1583">
+        <v>5364.83984375</v>
+      </c>
+      <c r="D1583">
+        <v>5265.56982421875</v>
+      </c>
+      <c r="E1583">
+        <v>5311.4501953125</v>
+      </c>
+      <c r="F1583">
+        <f t="shared" si="11"/>
+        <v>5.3114501953125002</v>
+      </c>
+      <c r="G1583">
+        <v>26669304</v>
+      </c>
+      <c r="H1583">
+        <v>26669304</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1584" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B1584">
+        <v>5297.02978515625</v>
+      </c>
+      <c r="C1584">
+        <v>5387.13818359375</v>
+      </c>
+      <c r="D1584">
+        <v>5279.84814453125</v>
+      </c>
+      <c r="E1584">
+        <v>5373.22021484375</v>
+      </c>
+      <c r="F1584">
+        <f t="shared" si="11"/>
+        <v>5.3732202148437498</v>
+      </c>
+      <c r="G1584">
+        <v>23403390</v>
+      </c>
+      <c r="H1584">
+        <v>23403390</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1585" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B1585">
+        <v>5372.22998046875</v>
+      </c>
+      <c r="C1585">
+        <v>5372.22998046875</v>
+      </c>
+      <c r="D1585">
+        <v>5182.35986328125</v>
+      </c>
+      <c r="E1585">
+        <v>5248.41796875</v>
+      </c>
+      <c r="F1585">
+        <f t="shared" si="11"/>
+        <v>5.2484179687500001</v>
+      </c>
+      <c r="G1585">
+        <v>27084242</v>
+      </c>
+      <c r="H1585">
+        <v>27084242</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1586" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B1586">
+        <v>5214.9638671875</v>
+      </c>
+      <c r="C1586">
+        <v>5261.52880859375</v>
+      </c>
+      <c r="D1586">
+        <v>5161.85009765625</v>
+      </c>
+      <c r="E1586">
+        <v>5219.919921875</v>
+      </c>
+      <c r="F1586">
+        <f t="shared" si="11"/>
+        <v>5.2199199218750003</v>
+      </c>
+      <c r="G1586">
+        <v>24922818</v>
+      </c>
+      <c r="H1586">
+        <v>24922818</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1587" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B1587">
+        <v>5227.57080078125</v>
+      </c>
+      <c r="C1587">
+        <v>5305.7490234375</v>
+      </c>
+      <c r="D1587">
+        <v>5205.31494140625</v>
+      </c>
+      <c r="E1587">
+        <v>5251.6240234375</v>
+      </c>
+      <c r="F1587">
+        <f t="shared" si="11"/>
+        <v>5.2516240234374996</v>
+      </c>
+      <c r="G1587">
+        <v>26071774</v>
+      </c>
+      <c r="H1587">
+        <v>26071774</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1588" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B1588">
+        <v>5268.4482421875</v>
+      </c>
+      <c r="C1588">
+        <v>5317.7421875</v>
+      </c>
+      <c r="D1588">
+        <v>5236.9150390625</v>
+      </c>
+      <c r="E1588">
+        <v>5317.2939453125</v>
+      </c>
+      <c r="F1588">
+        <f t="shared" si="11"/>
+        <v>5.3172939453124997</v>
+      </c>
+      <c r="G1588">
+        <v>29868516</v>
+      </c>
+      <c r="H1588">
+        <v>29868516</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1589" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B1589">
+        <v>5290.58984375</v>
+      </c>
+      <c r="C1589">
+        <v>5362.22900390625</v>
+      </c>
+      <c r="D1589">
+        <v>5264.6640625</v>
+      </c>
+      <c r="E1589">
+        <v>5266.59912109375</v>
+      </c>
+      <c r="F1589">
+        <f t="shared" si="11"/>
+        <v>5.2665991210937504</v>
+      </c>
+      <c r="G1589">
+        <v>27775096</v>
+      </c>
+      <c r="H1589">
+        <v>27775096</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1590" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B1590">
+        <v>5194.5771484375</v>
+      </c>
+      <c r="C1590">
+        <v>5280.00390625</v>
+      </c>
+      <c r="D1590">
+        <v>5160.9951171875</v>
+      </c>
+      <c r="E1590">
+        <v>5280.00390625</v>
+      </c>
+      <c r="F1590">
+        <f t="shared" si="11"/>
+        <v>5.2800039062500002</v>
+      </c>
+      <c r="G1590">
+        <v>29022858</v>
+      </c>
+      <c r="H1590">
+        <v>29022858</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1590"/>
+  <dimension ref="A1:H1611"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -40006,7 +40006,7 @@
         <v>5027.0078125</v>
       </c>
       <c r="F1468">
-        <f t="shared" ref="F1468:F1590" si="11">E1468/1000</f>
+        <f t="shared" ref="F1468:F1611" si="11">E1468/1000</f>
         <v>5.0270078125</v>
       </c>
       <c r="G1468">
@@ -43308,6 +43308,573 @@
       </c>
       <c r="H1590">
         <v>29022858</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1591" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B1591">
+        <v>5282.64013671875</v>
+      </c>
+      <c r="C1591">
+        <v>5284.37890625</v>
+      </c>
+      <c r="D1591">
+        <v>5207</v>
+      </c>
+      <c r="E1591">
+        <v>5223.5361328125</v>
+      </c>
+      <c r="F1591">
+        <f t="shared" si="11"/>
+        <v>5.2235361328124998</v>
+      </c>
+      <c r="G1591">
+        <v>27181514</v>
+      </c>
+      <c r="H1591">
+        <v>27181514</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1592" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B1592">
+        <v>5168.7080078125</v>
+      </c>
+      <c r="C1592">
+        <v>5171.02978515625</v>
+      </c>
+      <c r="D1592">
+        <v>5097.7548828125</v>
+      </c>
+      <c r="E1592">
+        <v>5115.42578125</v>
+      </c>
+      <c r="F1592">
+        <f t="shared" si="11"/>
+        <v>5.1154257812499999</v>
+      </c>
+      <c r="G1592">
+        <v>25054866</v>
+      </c>
+      <c r="H1592">
+        <v>25054866</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1593" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B1593">
+        <v>5153.31298828125</v>
+      </c>
+      <c r="C1593">
+        <v>5158.05078125</v>
+      </c>
+      <c r="D1593">
+        <v>5081.998046875</v>
+      </c>
+      <c r="E1593">
+        <v>5120.1298828125</v>
+      </c>
+      <c r="F1593">
+        <f t="shared" si="11"/>
+        <v>5.1201298828124999</v>
+      </c>
+      <c r="G1593">
+        <v>23629798</v>
+      </c>
+      <c r="H1593">
+        <v>23629798</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1594" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B1594">
+        <v>5158.958984375</v>
+      </c>
+      <c r="C1594">
+        <v>5183.283203125</v>
+      </c>
+      <c r="D1594">
+        <v>5041.36279296875</v>
+      </c>
+      <c r="E1594">
+        <v>5065.2578125</v>
+      </c>
+      <c r="F1594">
+        <f t="shared" si="11"/>
+        <v>5.0652578124999996</v>
+      </c>
+      <c r="G1594">
+        <v>27470134</v>
+      </c>
+      <c r="H1594">
+        <v>27470134</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1595" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B1595">
+        <v>5102.380859375</v>
+      </c>
+      <c r="C1595">
+        <v>5203.97802734375</v>
+      </c>
+      <c r="D1595">
+        <v>5099.4130859375</v>
+      </c>
+      <c r="E1595">
+        <v>5186.01708984375</v>
+      </c>
+      <c r="F1595">
+        <f t="shared" si="11"/>
+        <v>5.1860170898437499</v>
+      </c>
+      <c r="G1595">
+        <v>24149512</v>
+      </c>
+      <c r="H1595">
+        <v>24149512</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1596" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B1596">
+        <v>5184.64990234375</v>
+      </c>
+      <c r="C1596">
+        <v>5192.1640625</v>
+      </c>
+      <c r="D1596">
+        <v>5114.11279296875</v>
+      </c>
+      <c r="E1596">
+        <v>5129.09521484375</v>
+      </c>
+      <c r="F1596">
+        <f t="shared" si="11"/>
+        <v>5.1290952148437503</v>
+      </c>
+      <c r="G1596">
+        <v>24857530</v>
+      </c>
+      <c r="H1596">
+        <v>24857530</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1597" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B1597">
+        <v>5154.97314453125</v>
+      </c>
+      <c r="C1597">
+        <v>5154.97314453125</v>
+      </c>
+      <c r="D1597">
+        <v>5083.47119140625</v>
+      </c>
+      <c r="E1597">
+        <v>5123.0380859375</v>
+      </c>
+      <c r="F1597">
+        <f t="shared" si="11"/>
+        <v>5.1230380859375</v>
+      </c>
+      <c r="G1597">
+        <v>22010222</v>
+      </c>
+      <c r="H1597">
+        <v>22010222</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1598" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B1598">
+        <v>5086.6220703125</v>
+      </c>
+      <c r="C1598">
+        <v>5111.125</v>
+      </c>
+      <c r="D1598">
+        <v>5055.5439453125</v>
+      </c>
+      <c r="E1598">
+        <v>5074.171875</v>
+      </c>
+      <c r="F1598">
+        <f t="shared" si="11"/>
+        <v>5.0741718750000002</v>
+      </c>
+      <c r="G1598">
+        <v>18756890</v>
+      </c>
+      <c r="H1598">
+        <v>18756890</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1599" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B1599">
+        <v>5029.044921875</v>
+      </c>
+      <c r="C1599">
+        <v>5059.259765625</v>
+      </c>
+      <c r="D1599">
+        <v>4959.14599609375</v>
+      </c>
+      <c r="E1599">
+        <v>5041.30322265625</v>
+      </c>
+      <c r="F1599">
+        <f t="shared" si="11"/>
+        <v>5.04130322265625</v>
+      </c>
+      <c r="G1599">
+        <v>24637460</v>
+      </c>
+      <c r="H1599">
+        <v>24637460</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1600" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B1600">
+        <v>4995.841796875</v>
+      </c>
+      <c r="C1600">
+        <v>5065.46484375</v>
+      </c>
+      <c r="D1600">
+        <v>4970.61376953125</v>
+      </c>
+      <c r="E1600">
+        <v>5015.93115234375</v>
+      </c>
+      <c r="F1600">
+        <f t="shared" si="11"/>
+        <v>5.0159311523437502</v>
+      </c>
+      <c r="G1600">
+        <v>18472328</v>
+      </c>
+      <c r="H1600">
+        <v>18472328</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1601" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B1601">
+        <v>5006.55322265625</v>
+      </c>
+      <c r="C1601">
+        <v>5059.921875</v>
+      </c>
+      <c r="D1601">
+        <v>4958.9169921875</v>
+      </c>
+      <c r="E1601">
+        <v>4965.11279296875</v>
+      </c>
+      <c r="F1601">
+        <f t="shared" si="11"/>
+        <v>4.9651127929687497</v>
+      </c>
+      <c r="G1601">
+        <v>20625698</v>
+      </c>
+      <c r="H1601">
+        <v>20625698</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1602" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B1602">
+        <v>4956.421875</v>
+      </c>
+      <c r="C1602">
+        <v>5047.35107421875</v>
+      </c>
+      <c r="D1602">
+        <v>4923.10009765625</v>
+      </c>
+      <c r="E1602">
+        <v>5035.7958984375</v>
+      </c>
+      <c r="F1602">
+        <f t="shared" si="11"/>
+        <v>5.0357958984374998</v>
+      </c>
+      <c r="G1602">
+        <v>25002634</v>
+      </c>
+      <c r="H1602">
+        <v>25002634</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1603" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B1603">
+        <v>5025.7890625</v>
+      </c>
+      <c r="C1603">
+        <v>5083.2451171875</v>
+      </c>
+      <c r="D1603">
+        <v>5014.8740234375</v>
+      </c>
+      <c r="E1603">
+        <v>5024.30517578125</v>
+      </c>
+      <c r="F1603">
+        <f t="shared" si="11"/>
+        <v>5.02430517578125</v>
+      </c>
+      <c r="G1603">
+        <v>24101130</v>
+      </c>
+      <c r="H1603">
+        <v>24101130</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1604" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1604">
+        <v>5088.39404296875</v>
+      </c>
+      <c r="C1604">
+        <v>5138.19189453125</v>
+      </c>
+      <c r="D1604">
+        <v>5034.6669921875</v>
+      </c>
+      <c r="E1604">
+        <v>5112.5830078125</v>
+      </c>
+      <c r="F1604">
+        <f t="shared" si="11"/>
+        <v>5.1125830078124999</v>
+      </c>
+      <c r="G1604">
+        <v>26526058</v>
+      </c>
+      <c r="H1604">
+        <v>26526058</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1605" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1605">
+        <v>5136.328125</v>
+      </c>
+      <c r="C1605">
+        <v>5162.35400390625</v>
+      </c>
+      <c r="D1605">
+        <v>5097.2880859375</v>
+      </c>
+      <c r="E1605">
+        <v>5128.60009765625</v>
+      </c>
+      <c r="F1605">
+        <f t="shared" si="11"/>
+        <v>5.1286000976562498</v>
+      </c>
+      <c r="G1605">
+        <v>25711182</v>
+      </c>
+      <c r="H1605">
+        <v>25711182</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1606" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1606">
+        <v>5187.1650390625</v>
+      </c>
+      <c r="C1606">
+        <v>5225.5849609375</v>
+      </c>
+      <c r="D1606">
+        <v>5121.451171875</v>
+      </c>
+      <c r="E1606">
+        <v>5136.490234375</v>
+      </c>
+      <c r="F1606">
+        <f t="shared" si="11"/>
+        <v>5.1364902343749996</v>
+      </c>
+      <c r="G1606">
+        <v>27212378</v>
+      </c>
+      <c r="H1606">
+        <v>27212378</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1607" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1607">
+        <v>5143.8369140625</v>
+      </c>
+      <c r="C1607">
+        <v>5143.8369140625</v>
+      </c>
+      <c r="D1607">
+        <v>5097.69091796875</v>
+      </c>
+      <c r="E1607">
+        <v>5103.005859375</v>
+      </c>
+      <c r="F1607">
+        <f t="shared" si="11"/>
+        <v>5.1030058593750001</v>
+      </c>
+      <c r="G1607">
+        <v>21177718</v>
+      </c>
+      <c r="H1607">
+        <v>21177718</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1608" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1608">
+        <v>5080.10400390625</v>
+      </c>
+      <c r="C1608">
+        <v>5089.591796875</v>
+      </c>
+      <c r="D1608">
+        <v>4985.0361328125</v>
+      </c>
+      <c r="E1608">
+        <v>4985.0361328125</v>
+      </c>
+      <c r="F1608">
+        <f t="shared" si="11"/>
+        <v>4.9850361328124997</v>
+      </c>
+      <c r="G1608">
+        <v>20915886</v>
+      </c>
+      <c r="H1608">
+        <v>20915886</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1609" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1609">
+        <v>4958.64111328125</v>
+      </c>
+      <c r="C1609">
+        <v>4960.6279296875</v>
+      </c>
+      <c r="D1609">
+        <v>4774.56982421875</v>
+      </c>
+      <c r="E1609">
+        <v>4799.341796875</v>
+      </c>
+      <c r="F1609">
+        <f t="shared" si="11"/>
+        <v>4.7993417968749998</v>
+      </c>
+      <c r="G1609">
+        <v>24302134</v>
+      </c>
+      <c r="H1609">
+        <v>24302134</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1610" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1610">
+        <v>4793.47314453125</v>
+      </c>
+      <c r="C1610">
+        <v>4821.05419921875</v>
+      </c>
+      <c r="D1610">
+        <v>4780.6171875</v>
+      </c>
+      <c r="E1610">
+        <v>4798.2001953125</v>
+      </c>
+      <c r="F1610">
+        <f t="shared" si="11"/>
+        <v>4.7982001953125</v>
+      </c>
+      <c r="G1610">
+        <v>20340950</v>
+      </c>
+      <c r="H1610">
+        <v>20340950</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1611" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1611">
+        <v>4830.09423828125</v>
+      </c>
+      <c r="C1611">
+        <v>4832.64599609375</v>
+      </c>
+      <c r="D1611">
+        <v>4780.09912109375</v>
+      </c>
+      <c r="E1611">
+        <v>4796.033203125</v>
+      </c>
+      <c r="F1611">
+        <f t="shared" si="11"/>
+        <v>4.7960332031249999</v>
+      </c>
+      <c r="G1611">
+        <v>20198212</v>
+      </c>
+      <c r="H1611">
+        <v>20198212</v>
       </c>
     </row>
   </sheetData>
